--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:48:48+00:00</t>
+    <t>2026-03-19T07:57:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -394,8 +394,11 @@
     <t>Specimen.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">PractitionerRole {http://hl7.no/fhir/ig/ParekIG/StructureDefinition/parek-collector-pr}
-</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PractitionerRole {http://hl7.no/fhir/ig/ParekIG/StructureDefinition/parek-collector-pr}
+Device {http://hl7.no/fhir/ig/ParekIG/StructureDefinition/parek-device}</t>
   </si>
   <si>
     <t>Roles/organizations the practitioner is associated with</t>
@@ -408,6 +411,10 @@
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>administrative.individual</t>
@@ -2581,10 +2588,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>75</v>
@@ -2596,16 +2603,16 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2655,7 +2662,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2664,31 +2671,31 @@
         <v>77</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2707,16 +2714,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2766,7 +2773,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2778,13 +2785,13 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>75</v>
@@ -2792,14 +2799,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2818,19 +2825,19 @@
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2879,7 +2886,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2891,13 +2898,13 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>75</v>
@@ -2905,10 +2912,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2931,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2988,7 +2995,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3003,21 +3010,21 @@
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3043,10 +3050,10 @@
         <v>87</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3097,7 +3104,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3106,7 +3113,7 @@
         <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>75</v>
@@ -3115,7 +3122,7 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>75</v>
@@ -3123,14 +3130,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3149,16 +3156,16 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3196,19 +3203,19 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3220,13 +3227,13 @@
         <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>75</v>
@@ -3234,10 +3241,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3263,16 +3270,16 @@
         <v>105</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -3300,10 +3307,10 @@
         <v>109</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -3321,7 +3328,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3339,18 +3346,18 @@
         <v>75</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3373,19 +3380,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>75</v>
@@ -3410,13 +3417,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3434,7 +3441,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3452,18 +3459,18 @@
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3489,16 +3496,16 @@
         <v>99</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
@@ -3511,7 +3518,7 @@
         <v>75</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>75</v>
@@ -3547,7 +3554,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3565,18 +3572,18 @@
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3599,16 +3606,16 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3622,7 +3629,7 @@
         <v>75</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>75</v>
@@ -3658,7 +3665,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3667,7 +3674,7 @@
         <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>97</v>
@@ -3676,18 +3683,18 @@
         <v>75</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3710,13 +3717,13 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3767,7 +3774,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3785,18 +3792,18 @@
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3819,16 +3826,16 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3878,7 +3885,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3896,18 +3903,18 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3930,13 +3937,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3987,7 +3994,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4002,21 +4009,21 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4042,13 +4049,13 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4077,10 +4084,10 @@
         <v>109</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -4098,7 +4105,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4113,21 +4120,21 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4150,16 +4157,16 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4185,11 +4192,11 @@
         <v>75</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>75</v>
@@ -4207,7 +4214,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4222,21 +4229,21 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4259,17 +4266,17 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4318,7 +4325,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4333,10 +4340,10 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>75</v>
@@ -4344,10 +4351,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4373,10 +4380,10 @@
         <v>87</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4427,7 +4434,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4436,7 +4443,7 @@
         <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>75</v>
@@ -4445,7 +4452,7 @@
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -4453,14 +4460,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4479,16 +4486,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4526,19 +4533,19 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4550,13 +4557,13 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>75</v>
@@ -4564,10 +4571,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4590,16 +4597,16 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4649,7 +4656,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4658,7 +4665,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>97</v>
@@ -4667,7 +4674,7 @@
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>75</v>
@@ -4675,10 +4682,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4704,13 +4711,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4736,13 +4743,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4760,7 +4767,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4778,7 +4785,7 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>75</v>
@@ -4786,10 +4793,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4812,16 +4819,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4871,7 +4878,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4880,7 +4887,7 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>97</v>
@@ -4889,7 +4896,7 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>75</v>
@@ -4897,10 +4904,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4926,10 +4933,10 @@
         <v>87</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4980,7 +4987,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4989,7 +4996,7 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4998,7 +5005,7 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>75</v>
@@ -5006,14 +5013,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5032,16 +5039,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5079,19 +5086,19 @@
         <v>75</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5103,13 +5110,13 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>75</v>
@@ -5117,10 +5124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5146,16 +5153,16 @@
         <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -5183,10 +5190,10 @@
         <v>109</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -5204,7 +5211,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5222,18 +5229,18 @@
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5256,19 +5263,19 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5293,13 +5300,13 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -5317,7 +5324,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5335,18 +5342,18 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5372,16 +5379,16 @@
         <v>99</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5394,7 +5401,7 @@
         <v>75</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>75</v>
@@ -5410,7 +5417,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5428,7 +5435,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5446,18 +5453,18 @@
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5480,16 +5487,16 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5503,7 +5510,7 @@
         <v>75</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>75</v>
@@ -5539,7 +5546,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5548,7 +5555,7 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>97</v>
@@ -5557,18 +5564,18 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5591,13 +5598,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5648,7 +5655,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5666,18 +5673,18 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5700,16 +5707,16 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5759,7 +5766,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5777,18 +5784,18 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5811,16 +5818,16 @@
         <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5870,7 +5877,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5879,7 +5886,7 @@
         <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>97</v>
@@ -5888,7 +5895,7 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
@@ -5896,10 +5903,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5922,13 +5929,13 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5979,7 +5986,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5994,21 +6001,21 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6031,16 +6038,16 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6090,7 +6097,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6108,7 +6115,7 @@
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>75</v>
@@ -6116,10 +6123,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6142,16 +6149,16 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6201,7 +6208,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6216,21 +6223,21 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6256,10 +6263,10 @@
         <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6289,10 +6296,10 @@
         <v>109</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -6310,7 +6317,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6336,10 +6343,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6362,13 +6369,13 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6395,13 +6402,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6419,7 +6426,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6440,15 +6447,15 @@
         <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6471,13 +6478,13 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6528,7 +6535,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6546,7 +6553,7 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6554,10 +6561,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6580,13 +6587,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6637,7 +6644,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6646,7 +6653,7 @@
         <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>75</v>
@@ -6655,7 +6662,7 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -6663,14 +6670,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6689,16 +6696,16 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6748,7 +6755,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6760,13 +6767,13 @@
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
@@ -6774,14 +6781,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6800,19 +6807,19 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6861,7 +6868,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6873,13 +6880,13 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
@@ -6887,10 +6894,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6913,13 +6920,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6946,13 +6953,13 @@
         <v>75</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -6970,7 +6977,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>85</v>
@@ -6985,10 +6992,10 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>75</v>
@@ -6996,10 +7003,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7022,13 +7029,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7079,7 +7086,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>85</v>
@@ -7097,7 +7104,7 @@
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>75</v>
@@ -7105,10 +7112,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7131,13 +7138,13 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7188,7 +7195,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7206,18 +7213,18 @@
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7240,13 +7247,13 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7297,7 +7304,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7306,7 +7313,7 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>75</v>
@@ -7315,7 +7322,7 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>75</v>
@@ -7323,14 +7330,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7349,16 +7356,16 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7408,7 +7415,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7420,13 +7427,13 @@
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>75</v>
@@ -7434,14 +7441,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7460,19 +7467,19 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7521,7 +7528,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7533,13 +7540,13 @@
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>75</v>
@@ -7547,10 +7554,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7573,13 +7580,13 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7630,7 +7637,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7645,21 +7652,21 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7682,13 +7689,13 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7739,7 +7746,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7754,21 +7761,21 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7791,13 +7798,13 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7848,7 +7855,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7863,7 +7870,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7874,10 +7881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7900,13 +7907,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7957,7 +7964,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7975,18 +7982,18 @@
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8009,13 +8016,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8042,13 +8049,13 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -8066,7 +8073,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8084,18 +8091,18 @@
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8118,13 +8125,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8151,10 +8158,10 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>75</v>
@@ -8175,7 +8182,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8193,18 +8200,18 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8227,13 +8234,13 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8284,7 +8291,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8310,10 +8317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8336,16 +8343,16 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8371,13 +8378,13 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8395,7 +8402,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8413,18 +8420,18 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8447,19 +8454,19 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8484,13 +8491,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8508,7 +8515,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8529,15 +8536,15 @@
         <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8560,13 +8567,13 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8617,7 +8624,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8635,7 +8642,7 @@
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>75</v>
@@ -8643,10 +8650,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8669,13 +8676,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8726,7 +8733,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8735,7 +8742,7 @@
         <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>75</v>
@@ -8744,7 +8751,7 @@
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>75</v>
@@ -8752,14 +8759,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8778,16 +8785,16 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8837,7 +8844,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8849,13 +8856,13 @@
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -8863,14 +8870,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8889,19 +8896,19 @@
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8950,7 +8957,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8962,13 +8969,13 @@
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>75</v>
@@ -8976,10 +8983,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9002,13 +9009,13 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9059,7 +9066,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9077,7 +9084,7 @@
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>75</v>
@@ -9085,10 +9092,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9111,13 +9118,13 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9144,13 +9151,13 @@
         <v>75</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -9168,7 +9175,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9186,7 +9193,7 @@
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>75</v>
@@ -9194,10 +9201,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9220,13 +9227,13 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9277,7 +9284,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9295,18 +9302,18 @@
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9329,13 +9336,13 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9386,7 +9393,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9404,7 +9411,7 @@
         <v>75</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>75</v>
@@ -9412,10 +9419,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9438,13 +9445,13 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9495,7 +9502,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9513,7 +9520,7 @@
         <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>75</v>
@@ -9521,10 +9528,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9547,13 +9554,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9604,7 +9611,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9613,7 +9620,7 @@
         <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>75</v>
@@ -9622,7 +9629,7 @@
         <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>75</v>
@@ -9630,14 +9637,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9656,16 +9663,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9715,7 +9722,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9727,13 +9734,13 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>75</v>
@@ -9741,14 +9748,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9767,19 +9774,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9828,7 +9835,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9840,13 +9847,13 @@
         <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>75</v>
@@ -9854,10 +9861,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9880,13 +9887,13 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9937,7 +9944,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -9955,7 +9962,7 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>75</v>
@@ -9963,10 +9970,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9989,13 +9996,13 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10046,7 +10053,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10061,10 +10068,10 @@
         <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>75</v>
@@ -10072,10 +10079,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10098,13 +10105,13 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10155,7 +10162,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10173,18 +10180,18 @@
         <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10207,19 +10214,19 @@
         <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>75</v>
@@ -10244,13 +10251,13 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -10268,7 +10275,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10289,15 +10296,15 @@
         <v>75</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10320,13 +10327,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>49</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10377,7 +10384,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10395,10 +10402,10 @@
         <v>75</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T07:57:25+00:00</t>
+    <t>2026-03-19T11:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T11:47:55+00:00</t>
+    <t>2026-03-20T10:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T10:04:21+00:00</t>
+    <t>2026-03-20T11:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:14:53+00:00</t>
+    <t>2026-03-20T11:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:25:24+00:00</t>
+    <t>2026-03-20T11:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:48:45+00:00</t>
+    <t>2026-03-20T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:42:40+00:00</t>
+    <t>2026-03-20T12:57:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:57:31+00:00</t>
+    <t>2026-03-20T13:17:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -878,7 +878,7 @@
     <t>Specimen.subject.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-it-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-id-type-vs</t>
   </si>
   <si>
     <t>Specimen.subject.identifier.value</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:17:08+00:00</t>
+    <t>2026-04-10T11:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:25:48+00:00</t>
+    <t>2026-04-10T11:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:43:13+00:00</t>
+    <t>2026-04-10T11:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:51:44+00:00</t>
+    <t>2026-04-10T12:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:03:27+00:00</t>
+    <t>2026-04-10T12:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:17:42+00:00</t>
+    <t>2026-04-10T12:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:43:41+00:00</t>
+    <t>2026-04-10T12:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:51:31+00:00</t>
+    <t>2026-04-10T13:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:11:24+00:00</t>
+    <t>2026-04-13T12:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:24:04+00:00</t>
+    <t>2026-04-13T13:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T13:08:41+00:00</t>
+    <t>2026-04-15T12:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -878,7 +878,7 @@
     <t>Specimen.subject.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-id-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/person-public-id-type-vs</t>
   </si>
   <si>
     <t>Specimen.subject.identifier.value</t>

--- a/currentbuild/StructureDefinition-parek-specimen.xlsx
+++ b/currentbuild/StructureDefinition-parek-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
